--- a/src/data/HU4_EDA.xlsx
+++ b/src/data/HU4_EDA.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -58,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -558,11 +554,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>41745.53032407408</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>41745.53032407408</v>
+      <c r="G2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2014</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -596,12 +592,10 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>6.134957019724816</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>19.4113564708562</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -633,11 +627,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>41443.26747685186</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>41443.26747685186</v>
+      <c r="G3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2013</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -673,10 +667,8 @@
       <c r="R3" t="n">
         <v>19.53</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -708,11 +700,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>41665.95833333334</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>41665.95833333334</v>
+      <c r="G4" t="n">
+        <v>2014</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2014</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -748,10 +740,8 @@
       <c r="R4" t="n">
         <v>19.53</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -783,11 +773,11 @@
           <t>SOLUCIÓN</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>39476.95833333334</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>39476.95833333334</v>
+      <c r="G5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2008</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -823,10 +813,8 @@
       <c r="R5" t="n">
         <v>2.5</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -858,11 +846,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>41435.91666666666</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>41435.91666666666</v>
+      <c r="G6" t="n">
+        <v>2013</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2013</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -898,10 +886,8 @@
       <c r="R6" t="n">
         <v>1.97</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -933,11 +919,11 @@
           <t>PRODUCTO USO NASAL</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>35885.91666666666</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>35885.91666666666</v>
+      <c r="G7" t="n">
+        <v>1998</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1998</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -973,10 +959,8 @@
       <c r="R7" t="n">
         <v>21.4</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1008,11 +992,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>35976.91666666666</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>35976.91666666666</v>
+      <c r="G8" t="n">
+        <v>1998</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1998</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1046,12 +1030,10 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>32.28002473304019</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>12.20399863235396</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1083,11 +1065,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>37097.91666666666</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>37097.91666666666</v>
+      <c r="G9" t="n">
+        <v>2001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1123,10 +1105,8 @@
       <c r="R9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1158,11 +1138,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>37097.91666666666</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>37097.91666666666</v>
+      <c r="G10" t="n">
+        <v>2001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2001</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1198,10 +1178,8 @@
       <c r="R10" t="n">
         <v>17.59</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1233,11 +1211,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>37097.91666666666</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>37097.91666666666</v>
+      <c r="G11" t="n">
+        <v>2001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1273,10 +1251,8 @@
       <c r="R11" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1308,11 +1284,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>37097.91666666666</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>37097.91666666666</v>
+      <c r="G12" t="n">
+        <v>2001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1348,10 +1324,8 @@
       <c r="R12" t="n">
         <v>17.59</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1383,11 +1357,11 @@
           <t>COMPRIMIDO BUCODISPERSABLE</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>41654.95833333334</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>41654.95833333334</v>
+      <c r="G13" t="n">
+        <v>2014</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2014</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1423,10 +1397,8 @@
       <c r="R13" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1458,11 +1430,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>41406.91666666666</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>41406.91666666666</v>
+      <c r="G14" t="n">
+        <v>2013</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2013</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1498,10 +1470,8 @@
       <c r="R14" t="n">
         <v>26.4</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1512,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1533,11 +1503,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>39154.95833333334</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>39154.95833333334</v>
+      <c r="G15" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2007</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1573,10 +1543,8 @@
       <c r="R15" t="n">
         <v>36.62</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1587,7 +1555,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1608,11 +1576,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>39154.95833333334</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>39154.95833333334</v>
+      <c r="G16" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2007</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1648,10 +1616,8 @@
       <c r="R16" t="n">
         <v>73.25</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1662,7 +1628,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1683,11 +1649,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>39154.95833333334</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>39154.95833333334</v>
+      <c r="G17" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2007</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1723,10 +1689,8 @@
       <c r="R17" t="n">
         <v>9.16</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1737,7 +1701,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1758,11 +1722,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>39154.95833333334</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>39154.95833333334</v>
+      <c r="G18" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2007</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1798,10 +1762,8 @@
       <c r="R18" t="n">
         <v>18.31</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1812,7 +1774,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1833,11 +1795,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>39880.95833333334</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>39880.95833333334</v>
+      <c r="G19" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2009</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1873,10 +1835,8 @@
       <c r="R19" t="n">
         <v>36.62</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1887,7 +1847,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1908,11 +1868,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n">
-        <v>39880.95833333334</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>39880.95833333334</v>
+      <c r="G20" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2009</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1948,10 +1908,8 @@
       <c r="R20" t="n">
         <v>73.25</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1962,7 +1920,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1983,11 +1941,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>39880.95833333334</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>39880.95833333334</v>
+      <c r="G21" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2009</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2023,10 +1981,8 @@
       <c r="R21" t="n">
         <v>18.31</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2058,11 +2014,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>36522.95833333334</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>36522.95833333334</v>
+      <c r="G22" t="n">
+        <v>1999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1999</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2096,12 +2052,10 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>1.014395195761437</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>1.209441965519832</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2133,11 +2087,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G23" s="2" t="n">
-        <v>41443.26741898148</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>41443.26741898148</v>
+      <c r="G23" t="n">
+        <v>2013</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2013</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2173,10 +2127,8 @@
       <c r="R23" t="n">
         <v>19.53</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2208,11 +2160,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>36606.95833333334</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>36606.95833333334</v>
+      <c r="G24" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2000</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2246,12 +2198,10 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>12.1770639818571</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>16.87314186069718</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2283,11 +2233,11 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n">
-        <v>35976.91666666666</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>45454.64104166667</v>
+      <c r="G25" t="n">
+        <v>1998</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2024</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2321,12 +2271,10 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>7.191674970413283</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>21.63377393663744</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2358,11 +2306,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n">
-        <v>19875.95833333333</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>19875.95833333333</v>
+      <c r="G26" t="n">
+        <v>1954</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1954</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2396,12 +2344,10 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>19.2007727036536</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>17.74527901869944</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2412,7 +2358,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2433,11 +2379,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n">
-        <v>39252.91666666666</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>44966.51846064815</v>
+      <c r="G27" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2023</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2473,10 +2419,8 @@
       <c r="R27" t="n">
         <v>36.62</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2487,7 +2431,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2508,11 +2452,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n">
-        <v>39252.91666666666</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>44966.51803240741</v>
+      <c r="G28" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2023</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2548,10 +2492,8 @@
       <c r="R28" t="n">
         <v>73.25</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2562,7 +2504,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2583,11 +2525,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n">
-        <v>39252.91666666666</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>44966.51918981481</v>
+      <c r="G29" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2023</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2623,10 +2565,8 @@
       <c r="R29" t="n">
         <v>9.16</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2637,7 +2577,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2658,11 +2598,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n">
-        <v>39252.91666666666</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>44966.52112268518</v>
+      <c r="G30" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2023</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2698,10 +2638,8 @@
       <c r="R30" t="n">
         <v>18.31</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2733,11 +2671,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
-        <v>41703.45373842592</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>41703.45373842592</v>
+      <c r="G31" t="n">
+        <v>2014</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2014</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2771,12 +2709,10 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>20.36261591624755</v>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>18.21349152222157</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2808,11 +2744,11 @@
           <t>SOLUCIÓN</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
-        <v>38907.91666666666</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>38907.91666666666</v>
+      <c r="G32" t="n">
+        <v>2006</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2006</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2846,12 +2782,10 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>15.35168437967497</v>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>30.88084263127999</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2883,11 +2817,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
-        <v>40464.91666666666</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>40464.91666666666</v>
+      <c r="G33" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2010</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2923,10 +2857,8 @@
       <c r="R33" t="n">
         <v>1.97</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2958,11 +2890,11 @@
           <t>SOLUCIÓN</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
-        <v>39357.91666666666</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>39357.91666666666</v>
+      <c r="G34" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2007</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2998,10 +2930,8 @@
       <c r="R34" t="n">
         <v>2.5</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3033,11 +2963,11 @@
           <t>SOLUCIÓN</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
-        <v>40455.91666666666</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>46072.70087962963</v>
+      <c r="G35" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2026</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3071,12 +3001,10 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>20.72134587643805</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>5.064095939595505</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3108,11 +3036,11 @@
           <t>SOLUCIÓN</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>39959.91666666666</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>39959.91666666666</v>
+      <c r="G36" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2009</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3148,10 +3076,8 @@
       <c r="R36" t="n">
         <v>2.5</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3183,11 +3109,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
-        <v>40583.95833333334</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>44739.50465277778</v>
+      <c r="G37" t="n">
+        <v>2011</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2022</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3223,10 +3149,8 @@
       <c r="R37" t="n">
         <v>0.17</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3258,11 +3182,11 @@
           <t>CAPSULA</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
-        <v>42537.42425925926</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>42537.42425925926</v>
+      <c r="G38" t="n">
+        <v>2016</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2016</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3296,12 +3220,10 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>35.37650862143101</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>19.08795197841774</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3333,11 +3255,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
-        <v>38627.91666666666</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>45607.42717592593</v>
+      <c r="G39" t="n">
+        <v>2005</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2024</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -3373,10 +3295,8 @@
       <c r="R39" t="n">
         <v>1.97</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3408,11 +3328,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
-        <v>38000.95833333334</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>38000.95833333334</v>
+      <c r="G40" t="n">
+        <v>2004</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2004</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3448,10 +3368,8 @@
       <c r="R40" t="n">
         <v>2.06</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3483,11 +3401,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
-        <v>40701.91666666666</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>40701.91666666666</v>
+      <c r="G41" t="n">
+        <v>2011</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2011</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3523,10 +3441,8 @@
       <c r="R41" t="n">
         <v>1.97</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3558,11 +3474,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
-        <v>38895.91666666666</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>38895.91666666666</v>
+      <c r="G42" t="n">
+        <v>2006</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2006</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3598,10 +3514,8 @@
       <c r="R42" t="n">
         <v>2.06</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3633,11 +3547,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
-        <v>38301.95833333334</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>38301.95833333334</v>
+      <c r="G43" t="n">
+        <v>2004</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2004</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3673,10 +3587,8 @@
       <c r="R43" t="n">
         <v>1.97</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3708,11 +3620,11 @@
           <t>SOLUCIÓN</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
-        <v>39343.91666666666</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>39343.91666666666</v>
+      <c r="G44" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2007</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3748,10 +3660,8 @@
       <c r="R44" t="n">
         <v>2.5</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3783,11 +3693,11 @@
           <t>SOLUCIÓN</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
-        <v>39343.91666666666</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>39343.91666666666</v>
+      <c r="G45" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2007</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3823,10 +3733,8 @@
       <c r="R45" t="n">
         <v>2.5</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3858,11 +3766,11 @@
           <t>COMPRIMIDO LIBERACION MODIFICADA</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
-        <v>42551.91666666666</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>45208.58782407407</v>
+      <c r="G46" t="n">
+        <v>2016</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2023</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3898,10 +3806,8 @@
       <c r="R46" t="n">
         <v>1.89</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
+      <c r="S46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3933,11 +3839,11 @@
           <t>SOLUCIÓN</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
-        <v>23711.95833333333</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>23711.95833333333</v>
+      <c r="G47" t="n">
+        <v>1964</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1964</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3973,10 +3879,8 @@
       <c r="R47" t="n">
         <v>2</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4008,11 +3912,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
-        <v>23923.95833333333</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>23923.95833333333</v>
+      <c r="G48" t="n">
+        <v>1965</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1965</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4048,10 +3952,8 @@
       <c r="R48" t="n">
         <v>1.9</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4083,11 +3985,11 @@
           <t>INYECTABLE</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
-        <v>23711.95833333333</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>23711.95833333333</v>
+      <c r="G49" t="n">
+        <v>1964</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1964</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4123,10 +4025,8 @@
       <c r="R49" t="n">
         <v>2.58</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4158,11 +4058,11 @@
           <t>COMPRIMIDO BUCODISPERSABLE</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
-        <v>41340.95833333334</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>41340.95833333334</v>
+      <c r="G50" t="n">
+        <v>2013</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2013</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -4198,10 +4098,8 @@
       <c r="R50" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4233,11 +4131,11 @@
           <t>COMPRIMIDO BUCODISPERSABLE</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
-        <v>41382.91666666666</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>41382.91666666666</v>
+      <c r="G51" t="n">
+        <v>2013</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2013</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -4273,10 +4171,8 @@
       <c r="R51" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4308,11 +4204,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n">
-        <v>41383.54265046296</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>41383.54265046296</v>
+      <c r="G52" t="n">
+        <v>2013</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2013</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -4348,10 +4244,8 @@
       <c r="R52" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4383,11 +4277,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n">
-        <v>39190.91666666666</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>45673.586875</v>
+      <c r="G53" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2025</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -4423,10 +4317,8 @@
       <c r="R53" t="n">
         <v>12.18</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4458,11 +4350,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
-        <v>24138.95833333333</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>24138.95833333333</v>
+      <c r="G54" t="n">
+        <v>1966</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1966</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -4498,10 +4390,8 @@
       <c r="R54" t="n">
         <v>1.42</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
+      <c r="S54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -4533,11 +4423,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
-        <v>24138.95833333333</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>24138.95833333333</v>
+      <c r="G55" t="n">
+        <v>1966</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1966</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -4573,10 +4463,8 @@
       <c r="R55" t="n">
         <v>1.98</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
+      <c r="S55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -4587,7 +4475,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4608,11 +4496,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
-        <v>39645.91666666666</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>44582.61846064815</v>
+      <c r="G56" t="n">
+        <v>2008</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2022</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -4646,12 +4534,10 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>15.08779266091637</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>15.06305417095558</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -4662,7 +4548,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4683,11 +4569,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
-        <v>39645.91666666666</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>44582.6184375</v>
+      <c r="G57" t="n">
+        <v>2008</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2022</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -4721,12 +4607,10 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>33.19391356473375</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>36.54496821047265</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -4737,7 +4621,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4758,11 +4642,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n">
-        <v>39645.91666666666</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>44582.61849537037</v>
+      <c r="G58" t="n">
+        <v>2008</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2022</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -4796,12 +4680,10 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>37.94081130936505</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>12.85498888586537</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4812,7 +4694,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4833,11 +4715,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G59" s="2" t="n">
-        <v>39645.91666666666</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>44515.70206018518</v>
+      <c r="G59" t="n">
+        <v>2008</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2021</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -4871,12 +4753,10 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>26.93112528035831</v>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>33.39289917670567</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -4887,7 +4767,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4908,11 +4788,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n">
-        <v>39195.91666666666</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>39195.91666666666</v>
+      <c r="G60" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2007</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -4946,12 +4826,10 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>20.04072346790348</v>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>25.61865261164361</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -4962,7 +4840,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4983,11 +4861,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
-        <v>39195.91666666666</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>39195.91666666666</v>
+      <c r="G61" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2007</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -5021,12 +4899,10 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>39.74933142832448</v>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>17.51742269068619</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -5037,7 +4913,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5058,11 +4934,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
-        <v>39195.91666666666</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>39195.91666666666</v>
+      <c r="G62" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2007</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -5096,12 +4972,10 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>3.914171447037968</v>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>15.85538368283695</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -5112,7 +4986,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5133,11 +5007,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n">
-        <v>39195.91666666666</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>39195.91666666666</v>
+      <c r="G63" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2007</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -5171,12 +5045,10 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>28.89540272640733</v>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>11.86915051866762</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -5187,7 +5059,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5208,11 +5080,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G64" s="2" t="n">
-        <v>39414.95833333334</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>39414.95833333334</v>
+      <c r="G64" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H64" t="n">
+        <v>2007</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5246,12 +5118,10 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>31.3172461312504</v>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>0.7467759699793388</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5262,7 +5132,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5283,11 +5153,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n">
-        <v>39414.95833333334</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>39414.95833333334</v>
+      <c r="G65" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2007</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5321,12 +5191,10 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>34.23250550372268</v>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>35.52014658393926</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5337,7 +5205,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5358,11 +5226,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n">
-        <v>39414.95833333334</v>
-      </c>
-      <c r="H66" s="2" t="n">
-        <v>39414.95833333334</v>
+      <c r="G66" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2007</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -5396,12 +5264,10 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>36.96994888453525</v>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>35.92450456628779</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5412,7 +5278,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5433,11 +5299,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n">
-        <v>39880.95833333334</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>45356.63097222222</v>
+      <c r="G67" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2024</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5471,12 +5337,10 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>34.72911821952497</v>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+        <v>22.89854859379742</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -5487,7 +5351,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5508,11 +5372,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G68" s="2" t="n">
-        <v>39243.91666666666</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>45786.51597222222</v>
+      <c r="G68" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2025</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5548,10 +5412,8 @@
       <c r="R68" t="n">
         <v>36.62</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -5562,7 +5424,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5583,11 +5445,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G69" s="2" t="n">
-        <v>39243.91666666666</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>45811.65752314815</v>
+      <c r="G69" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2025</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -5623,10 +5485,8 @@
       <c r="R69" t="n">
         <v>73.25</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -5637,7 +5497,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5658,11 +5518,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G70" s="2" t="n">
-        <v>39243.91666666666</v>
-      </c>
-      <c r="H70" s="2" t="n">
-        <v>45673.58284722222</v>
+      <c r="G70" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H70" t="n">
+        <v>2025</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -5698,10 +5558,8 @@
       <c r="R70" t="n">
         <v>9.16</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -5712,7 +5570,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TOPIRAMATO</t>
+          <t xml:space="preserve">TOPIRAMATO </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5733,11 +5591,11 @@
           <t>COMPRIMIDO</t>
         </is>
       </c>
-      <c r="G71" s="2" t="n">
-        <v>39243.91666666666</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>45673.58277777778</v>
+      <c r="G71" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2025</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -5773,10 +5631,8 @@
       <c r="R71" t="n">
         <v>18.31</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
+      <c r="S71" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
